--- a/products/back-to-school-command-center/Back_To_School_Command_Center.xlsx
+++ b/products/back-to-school-command-center/Back_To_School_Command_Center.xlsx
@@ -608,7 +608,12 @@
           </val>
         </ser>
         <dLbls>
-          <showPercent val="1"/>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
         </dLbls>
         <firstSliceAng val="0"/>
         <holeSize val="10"/>
@@ -775,7 +780,12 @@
           </val>
         </ser>
         <dLbls>
-          <showPercent val="1"/>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
         </dLbls>
         <firstSliceAng val="0"/>
         <holeSize val="10"/>
@@ -922,7 +932,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>7</col>
       <colOff>0</colOff>
       <row>13</row>
       <rowOff>0</rowOff>
@@ -6420,7 +6430,7 @@
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
@@ -6457,7 +6467,7 @@
         </is>
       </c>
       <c r="C6" s="17" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
@@ -6492,7 +6502,7 @@
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
@@ -6527,7 +6537,7 @@
         </is>
       </c>
       <c r="C8" s="17" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
@@ -6558,7 +6568,7 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
@@ -6593,7 +6603,7 @@
         </is>
       </c>
       <c r="C10" s="17" t="n">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
@@ -6628,7 +6638,7 @@
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -6659,7 +6669,7 @@
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
@@ -6694,7 +6704,7 @@
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
@@ -6727,7 +6737,7 @@
         </is>
       </c>
       <c r="C14" s="17" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
